--- a/Team-Data/2013-14/2-6-2013-14.xlsx
+++ b/Team-Data/2013-14/2-6-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
@@ -781,7 +848,7 @@
         <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -960,7 +1027,7 @@
         <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
         <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.468</v>
+        <v>0.457</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="J4" t="n">
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="N4" t="n">
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="S4" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T4" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="U4" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
         <v>14.6</v>
@@ -1091,25 +1158,25 @@
         <v>4</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.7</v>
+        <v>97.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.4</v>
+        <v>-2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
@@ -1118,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
@@ -1130,13 +1197,13 @@
         <v>14</v>
       </c>
       <c r="AM4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN4" t="n">
         <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
         <v>8</v>
@@ -1145,16 +1212,16 @@
         <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
@@ -1166,19 +1233,19 @@
         <v>24</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
         <v>26</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="AI5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
         <v>25</v>
@@ -1360,7 +1427,7 @@
         <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>48.8</v>
@@ -1413,10 +1480,10 @@
         <v>0.422</v>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N6" t="n">
         <v>0.335</v>
@@ -1425,13 +1492,13 @@
         <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.768</v>
+        <v>0.765</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
         <v>32.5</v>
@@ -1443,40 +1510,40 @@
         <v>22</v>
       </c>
       <c r="V6" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
         <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
@@ -1485,7 +1552,7 @@
         <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
@@ -1506,7 +1573,7 @@
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
         <v>7</v>
@@ -1536,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>26</v>
@@ -1661,7 +1728,7 @@
         <v>27</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1901,7 @@
         <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2113,7 @@
         <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
@@ -2082,10 +2149,10 @@
         <v>29</v>
       </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
         <v>14</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.592</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,7 +2384,7 @@
         <v>38.8</v>
       </c>
       <c r="J11" t="n">
-        <v>84.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="K11" t="n">
         <v>0.457</v>
@@ -2326,16 +2393,16 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.382</v>
+        <v>0.38</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0.738</v>
@@ -2344,16 +2411,16 @@
         <v>11.2</v>
       </c>
       <c r="S11" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="T11" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U11" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V11" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W11" t="n">
         <v>7.8</v>
@@ -2365,19 +2432,19 @@
         <v>4.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>102.9</v>
+        <v>103</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2398,7 +2465,7 @@
         <v>6</v>
       </c>
       <c r="AK11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL11" t="n">
         <v>5</v>
@@ -2413,7 +2480,7 @@
         <v>25</v>
       </c>
       <c r="AP11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>23</v>
@@ -2452,7 +2519,7 @@
         <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>18</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>8.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2759,7 +2826,7 @@
         <v>20</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
@@ -3153,10 +3220,10 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV15" t="n">
         <v>18</v>
@@ -3168,7 +3235,7 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3308,7 +3375,7 @@
         <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3478,7 +3545,7 @@
         <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
         <v>8</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3684,7 +3751,7 @@
         <v>20</v>
       </c>
       <c r="AO18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
@@ -3702,7 +3769,7 @@
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
@@ -3908,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -4015,10 +4082,10 @@
         <v>-1.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
@@ -4242,7 +4309,7 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4646,7 @@
         <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
         <v>19</v>
@@ -4603,7 +4670,7 @@
         <v>14</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>9</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4837,7 @@
         <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH25" t="n">
         <v>24</v>
@@ -4946,7 +5013,7 @@
         <v>9</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>4</v>
@@ -4994,7 +5061,7 @@
         <v>22</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -5107,13 +5174,13 @@
         <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
       </c>
       <c r="AF26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
         <v>36</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.49</v>
+        <v>0.491</v>
       </c>
       <c r="L28" t="n">
         <v>8.1</v>
@@ -5423,28 +5490,28 @@
         <v>20.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="O28" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="P28" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
         <v>9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U28" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="V28" t="n">
         <v>14.7</v>
@@ -5453,49 +5520,49 @@
         <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.9</v>
+        <v>104.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
       </c>
       <c r="AF28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP28" t="n">
         <v>30</v>
@@ -5513,13 +5580,13 @@
         <v>11</v>
       </c>
       <c r="AR28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5531,7 +5598,7 @@
         <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>17</v>
@@ -5543,7 +5610,7 @@
         <v>25</v>
       </c>
       <c r="BB28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5704,7 +5771,7 @@
         <v>13</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5871,7 +5938,7 @@
         <v>23</v>
       </c>
       <c r="AP30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6080,7 +6147,7 @@
         <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-6-2013-14</t>
+          <t>2014-02-06</t>
         </is>
       </c>
     </row>
